--- a/Test Cases/ManagerReferral_TestCases.xlsx
+++ b/Test Cases/ManagerReferral_TestCases.xlsx
@@ -4,19 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6615"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6615" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ManagerReferralPage_TestCases" sheetId="1" r:id="rId1"/>
     <sheet name="ManagerReferralReport_TestCases" sheetId="2" r:id="rId2"/>
-    <sheet name="CandidateAuth_TestCases" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="443">
   <si>
     <t>S.No</t>
   </si>
@@ -1553,597 +1552,13 @@
     <t>headerLogo: present; title/label/button/footer text: OK; column headers: Referral date, iTAP Number, Candidate name, Email ID, Mobile number, Aadhaar number present, but "Initial feedback" column header is misspelled "Initital feedback" on the live page.</t>
   </si>
   <si>
-    <t>Verify all UI components are present on the Candidate Sign In page</t>
-  </si>
-  <si>
-    <t>Verifying that Username, Password, the acknowledgment checkbox, Sign in button, Forgot password link, and Create a new one link are all present/locatable</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Locate the Username (Aadhaar Number) field
-3. Locate the Password field
-4. Locate the acknowledgment checkbox
-5. Locate the Sign in button
-6. Locate the Forgot password link
-7. Locate the Create a new one link</t>
-  </si>
-  <si>
-    <t>All 6 components should be present and visible: Username, Password, acknowledgment checkbox, Sign in button, Forgot password link, Create a new one link</t>
-  </si>
-  <si>
-    <t>usernameInput: present; passwordInput: present; acknowledgmentCheckbox: present; signInButton: present; forgotPasswordLink: present; createAccountLink: present.</t>
-  </si>
-  <si>
-    <t>Verify Sign In succeeds with valid, existing credentials</t>
-  </si>
-  <si>
-    <t>Verifying that signing in with a real account's correct Aadhaar Number and Password succeeds and proceeds into the Application Form</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: 989127033381 (existing account), Password: &lt;correct&gt;</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter the existing account's Username and Password
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Sign in should succeed and the candidate should be taken into the Application Form</t>
-  </si>
-  <si>
-    <t>reached Application Form=true</t>
-  </si>
-  <si>
-    <t>Verify Sign In rejects empty Username</t>
-  </si>
-  <si>
-    <t>Verifying that leaving Username blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: (blank), Password: Passw0rd1</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Leave Username blank, enter a Password
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Username should be rejected with a validation message</t>
-  </si>
-  <si>
-    <t>username aria-invalid=true, message="Please enter valid Aadhaar number"</t>
-  </si>
-  <si>
-    <t>Verify Sign In rejects empty Password</t>
-  </si>
-  <si>
-    <t>Verifying that leaving Password blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: 989127033381, Password: (blank)</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter Username, leave Password blank
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Password should be rejected with a validation message</t>
-  </si>
-  <si>
-    <t>password aria-invalid=true</t>
-  </si>
-  <si>
-    <t>Verify Sign In rejects a non-numeric Username</t>
-  </si>
-  <si>
-    <t>Verifying that an alphabetic Username is rejected since Aadhaar Number must be digits only</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: abcdefghijkl</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter Username "abcdefghijkl"
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Verify Sign In rejects a Username shorter than 12 digits</t>
-  </si>
-  <si>
-    <t>Verifying an 11-digit Username is rejected for not matching the required 12-digit Aadhaar length</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: 12345678901 (11 digits)</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter Username "12345678901" (11 digits)
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Username should be rejected with a validation message for not being 12 digits</t>
-  </si>
-  <si>
-    <t>Verify Sign In Username field restricts input beyond 12 digits</t>
-  </si>
-  <si>
-    <t>Verifying the field caps input at the maximum 12-digit Aadhaar length</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: 1234567890123 (13 digits)</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter Username "1234567890123" (13 digits)
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Input should be capped at 12 digits; the resulting value should still be validated (here, no matching account)</t>
-  </si>
-  <si>
-    <t>Typed 13 chars; field held 12 (maxlength=12). modal="×
-Information
-We couldn’t find your account. Please sign up to get started.
-OK"</t>
-  </si>
-  <si>
-    <t>Verify Sign In requires the acknowledgment checkbox</t>
-  </si>
-  <si>
-    <t>Verifying that submitting with valid credentials but an unchecked acknowledgment checkbox is blocked</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: 989127033381, Password: valid, checkbox: unchecked</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter valid Username and Password
-3. Leave the acknowledgment checkbox unchecked
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Form should not sign in; a message should prompt the user to acknowledge the terms</t>
-  </si>
-  <si>
-    <t>modal="×
-Information
-Please acknowledge the terms before signing in
-OK"</t>
-  </si>
-  <si>
-    <t>Verify Sign In shows an appropriate message for a non-existent account</t>
-  </si>
-  <si>
-    <t>Verifying that valid-format credentials for an account that does not exist show a clear "not found" message</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: &lt;freshly generated, guaranteed unused&gt; (valid format, no account)</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter a valid-format Username with no matching account
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>A message should indicate no account was found and suggest signing up</t>
-  </si>
-  <si>
-    <t>modal="×
-Information
-We couldn’t find your account. Please sign up to get started.
-OK"</t>
-  </si>
-  <si>
-    <t>Verify Sign In shows an appropriate message for a wrong password on an existing account</t>
-  </si>
-  <si>
-    <t>Verifying that a correct Username with an incorrect Password is rejected with a clear message, and does not disclose whether the field at fault is username or password</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: 989127033381 (existing), Password: WrongPass9</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter the existing account's Username with an incorrect Password
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>A message should indicate the username or password is incorrect, without signing in</t>
-  </si>
-  <si>
-    <t>modal="×
-Information
-Your Username or Password is incorrect
-OK"</t>
-  </si>
-  <si>
-    <t>Verify Sign In Username field against script/SQL injection input</t>
-  </si>
-  <si>
-    <t>Verifying that the field safely rejects script tags or SQL injection style input without executing or breaking the application</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin | Username: "&lt;script&gt;alert(1)&lt;/script&gt;" / "' OR '1'='1"</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Enter Username as a script tag or SQL injection string
-3. Check the acknowledgment checkbox
-4. Click Sign in</t>
-  </si>
-  <si>
-    <t>Input should be rejected as an invalid Aadhaar format; no script execution or application error should occur</t>
-  </si>
-  <si>
-    <t>username aria-invalid=true, message="Please enter valid Aadhaar number" secondary: username aria-invalid=true, message="Please enter valid Aadhaar number"</t>
-  </si>
-  <si>
-    <t>Verify all UI components are present on the Candidate Sign Up modal</t>
-  </si>
-  <si>
-    <t>Verifying that Aadhaar Number, Email, New Password, Confirm Password, Manager Reference ID, the acknowledgment checkbox, Sign Up button, close button, and the Sign In toggle link are all present/locatable</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; click "Create a new one"</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Click "Create a new one" to open the Sign Up modal
-3. Locate the Aadhaar Number field
-4. Locate the Email field
-5. Locate the New Password - Mankind ID field
-6. Locate the Confirm Password - Mankind ID field
-7. Locate the Manager Reference ID field
-8. Locate the acknowledgment checkbox
-9. Locate the Sign Up button
-10. Locate the close (X) button
-11. Locate the "Already have an account? Sign In" link</t>
-  </si>
-  <si>
-    <t>All 9 components should be present and visible in the Sign Up modal: Aadhaar Number, Email, New Password, Confirm Password, Manager Reference ID, acknowledgment checkbox, Sign Up button, close button, Sign In toggle link</t>
-  </si>
-  <si>
-    <t>aadhaarNumberInput: present; emailInput: present; newPasswordInput: present; confirmPasswordInput: present; managerReferenceIdInput: present; signUpAcknowledgmentCheckbox: present; signUpButton: present; signUpCloseButton: present; signUpToSignInLink: present.</t>
-  </si>
-  <si>
-    <t>Verify Sign Up succeeds with fully valid data and proceeds to the Application Form</t>
-  </si>
-  <si>
-    <t>Verifying that a fresh Aadhaar Number/Email, a policy-compliant matching password, and a valid Manager Reference ID together complete Sign Up</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Aadhaar: &lt;fresh&gt;, Email: &lt;fresh&gt;, Password: Passw0rd1, Reference ID: 10001556</t>
-  </si>
-  <si>
-    <t>1. Open the candidate login link
-2. Click Create a new one
-3. Enter a fresh Aadhaar Number and Email
-4. Enter matching, policy-compliant New/Confirm Password
-5. Enter Reference ID "10001556"
-6. Check the acknowledgment checkbox
-7. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Sign Up should succeed and the candidate should be taken into the Application Form</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects empty Aadhaar Number</t>
-  </si>
-  <si>
-    <t>Verifying that leaving Aadhaar Number blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Aadhaar: (blank), other fields valid</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Leave Aadhaar Number blank, fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Aadhaar Number should be rejected with a validation message</t>
-  </si>
-  <si>
-    <t>aadhaar aria-invalid=true, message="Enter Valid Aadhaar Number"</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects empty Email</t>
-  </si>
-  <si>
-    <t>Verifying that leaving Email blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Email: (blank), other fields valid</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Leave Email blank, fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Email should be rejected with "Enter Email ID"</t>
-  </si>
-  <si>
-    <t>email aria-invalid=true, message="Enter Email ID"</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects empty New Password</t>
-  </si>
-  <si>
-    <t>Verifying that leaving New Password blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | New Password: (blank), other fields valid</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Leave New Password blank, fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>New Password should be rejected with "Enter Password"</t>
-  </si>
-  <si>
-    <t>newPassword aria-invalid=true</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects empty Confirm Password</t>
-  </si>
-  <si>
-    <t>Verifying that leaving Confirm Password blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Confirm Password: (blank), other fields valid</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Leave Confirm Password blank, fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Confirm Password should be rejected with "Enter Password"</t>
-  </si>
-  <si>
-    <t>confirmPassword aria-invalid=true</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects empty Manager Reference ID</t>
-  </si>
-  <si>
-    <t>Verifying that leaving Manager Reference ID blank is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Reference ID: (blank), other fields valid</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Leave Manager Reference ID blank, fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Manager Reference ID should be rejected mentioning the Division Code</t>
-  </si>
-  <si>
-    <t>referenceId aria-invalid=true, message="Manager Reference ID does not contain the Division Code. Please contact your referrer."</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects a non-numeric Aadhaar Number</t>
-  </si>
-  <si>
-    <t>Verifying that an alphabetic Aadhaar Number is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Aadhaar: abcdefghijkl</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter Aadhaar Number "abcdefghijkl", fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects an Aadhaar Number shorter than 12 digits</t>
-  </si>
-  <si>
-    <t>Verifying an 11-digit Aadhaar Number is rejected for not matching the required length</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Aadhaar: 12345678901 (11 digits)</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter Aadhaar Number "12345678901" (11 digits), fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Aadhaar Number should be rejected with a validation message for not being 12 digits</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects an invalid Email format</t>
-  </si>
-  <si>
-    <t>Verifying that a malformed email address is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Email: notanemail</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter Email "notanemail", fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Email should be rejected with "Please enter a valid email address."</t>
-  </si>
-  <si>
-    <t>email aria-invalid=true, message="Please enter a valid email address."</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects a New Password with no digit</t>
-  </si>
-  <si>
-    <t>Verifying the password policy (8 chars + at least 1 digit) rejects an all-letters password</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | New/Confirm Password: Password (no digit)</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter New/Confirm Password "Password" (8 letters, no digit), fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>A password policy modal should be shown: "Check Password policy 8 Character and at least 1 digit should be there."</t>
-  </si>
-  <si>
-    <t>modal="×
-Information
-Check Password policy 8 Character and at least 1 digit should be there.
-OK"</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects a New Password shorter than 8 characters</t>
-  </si>
-  <si>
-    <t>Verifying the password policy rejects a password shorter than the minimum 8 characters</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | New/Confirm Password: Pass1 (5 chars)</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter New/Confirm Password "Pass1" (5 chars), fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>The same password policy modal should be shown for a too-short password</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects a mismatched Confirm Password</t>
-  </si>
-  <si>
-    <t>Verifying that a Confirm Password different from New Password is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | New Password: Passw0rd1, Confirm Password: Passw0rd2</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter different, both policy-valid New Password and Confirm Password
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Confirm Password should be rejected with "New Password and Confirm Password must be same"</t>
-  </si>
-  <si>
-    <t>confirmPassword aria-invalid=true, message="New Password and Confirm Password must be same"</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects a well-formed but unmatched Manager Reference ID</t>
-  </si>
-  <si>
-    <t>Verifying an 8-digit code that is not a real/matching SAP code is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Reference ID: 99999999 (valid shape, not a real code)</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter Reference ID "99999999" (8 digits, not a real code), fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Manager Reference ID should be rejected, directing the candidate to verify it with their referring manager</t>
-  </si>
-  <si>
-    <t>referenceId aria-invalid=true, message="Please enter correct Manager Reference ID as provided by your referring manager or refer to the Sign-up email that you have received"</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects a non-numeric Manager Reference ID</t>
-  </si>
-  <si>
-    <t>Verifying a non-numeric Reference ID is rejected the same way as a well-formed-but-unmatched one</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Reference ID: abcd1234</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter Reference ID "abcd1234", fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Manager Reference ID should be rejected the same way as a well-formed but unmatched code</t>
-  </si>
-  <si>
-    <t>Verify Sign Up requires the acknowledgment checkbox</t>
-  </si>
-  <si>
-    <t>Verifying that submitting with otherwise-valid data but an unchecked acknowledgment checkbox is blocked</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | all fields valid, checkbox unchecked</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Fill every field validly
-3. Leave the acknowledgment checkbox unchecked
-4. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Form should not sign up; a message should prompt the user to acknowledge the terms</t>
-  </si>
-  <si>
-    <t>Verify Sign Up rejects an already-registered Aadhaar Number</t>
-  </si>
-  <si>
-    <t>Verifying that signing up again with an Aadhaar Number that already has an account is rejected</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Aadhaar: 989127033381 (already registered)</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter the already-registered Aadhaar Number with a fresh Email
-3. Fill remaining fields validly
-4. Click Sign Up</t>
-  </si>
-  <si>
-    <t>A message should indicate an account with this Aadhaar number already exists</t>
-  </si>
-  <si>
-    <t>modal="×
-Information
-An account with this aadhaar number already exists. Please log in or use the ‘Forgot Password’ option to reset your credentials.
-OK"</t>
-  </si>
-  <si>
-    <t>Verify Sign Up Email field against script/SQL injection input</t>
-  </si>
-  <si>
-    <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/candidatelogin -&gt; Create a new one | Email: "&lt;script&gt;alert(1)&lt;/script&gt;" / "' OR '1'='1"</t>
-  </si>
-  <si>
-    <t>1. Open Sign Up
-2. Enter Email as a script tag or SQL injection string, fill other fields validly
-3. Click Sign Up</t>
-  </si>
-  <si>
-    <t>Input should be rejected as an invalid email format; no script execution or application error should occur</t>
-  </si>
-  <si>
-    <t>email aria-invalid=true, message="Please enter a valid email address." secondary: email aria-invalid=true, message="Please enter a valid email address."</t>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
   </si>
 </sst>
 </file>
@@ -2493,7 +1908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
@@ -2510,7 +1925,7 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2541,8 +1956,11 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2574,7 +1992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2605,8 +2023,11 @@
       <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2638,7 +2059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2670,7 +2091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2702,7 +2123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2734,7 +2155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2766,7 +2187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2798,7 +2219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2830,7 +2251,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2862,7 +2283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2894,7 +2315,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2926,7 +2347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -2958,7 +2379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -2990,7 +2411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -3022,7 +2443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -3054,7 +2475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -3086,7 +2507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -3118,7 +2539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>20</v>
       </c>
@@ -3149,8 +2570,11 @@
       <c r="J20" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K20" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>21</v>
       </c>
@@ -3181,8 +2605,11 @@
       <c r="J21" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -3214,7 +2641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -3246,7 +2673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -3278,7 +2705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -3310,7 +2737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -3342,7 +2769,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -3374,7 +2801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -3406,7 +2833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -3438,7 +2865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -3470,7 +2897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -3502,7 +2929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -3534,7 +2961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -3566,7 +2993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -3598,7 +3025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>35</v>
       </c>
@@ -3629,8 +3056,11 @@
       <c r="J35" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="3" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>36</v>
       </c>
@@ -3661,8 +3091,11 @@
       <c r="J36" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -3694,7 +3127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -3726,7 +3159,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -3758,7 +3191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -3790,7 +3223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -3822,7 +3255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -3854,7 +3287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -3886,7 +3319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -3918,7 +3351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -3950,7 +3383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -3982,7 +3415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -4014,7 +3447,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -4206,7 +3639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="225" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4246,7 +3679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1" customWidth="1"/>
@@ -4261,7 +3694,7 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4292,8 +3725,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4325,7 +3761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4357,7 +3793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4389,7 +3825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4421,7 +3857,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4453,7 +3889,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4485,7 +3921,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4517,7 +3953,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4549,7 +3985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="210" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="210" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4581,7 +4017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4613,7 +4049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4645,7 +4081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4677,7 +4113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4709,7 +4145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4741,7 +4177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4773,7 +4209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="4" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="4" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -4805,7 +4241,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="210" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="210" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -4837,7 +4273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="3" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="3" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4868,989 +4304,8 @@
       <c r="J19" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="9.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="50" style="1" customWidth="1"/>
-    <col min="7" max="7" width="45.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="55.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="K19" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="210" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Test Cases/ManagerReferral_TestCases.xlsx
+++ b/Test Cases/ManagerReferral_TestCases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6615" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ManagerReferralPage_TestCases" sheetId="1" r:id="rId1"/>
-    <sheet name="ManagerReferralReport_TestCases" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="ManagerReferralPage_TestCases" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="ManagerReferralReport_TestCases" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -47,6 +47,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>TC_01</t>
   </si>
   <si>
@@ -62,7 +65,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: Prasoon</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name "Prasoon"
 3. Proceed/submit the form</t>
   </si>
@@ -91,7 +94,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: Prasoon123</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name "Prasoon123" 
 3. enter any valid mobile number eg. 9864643241         .
 4. enter reference id - 10001556    
@@ -107,6 +110,9 @@
     <t>Failed</t>
   </si>
   <si>
+    <t>P1</t>
+  </si>
+  <si>
     <t>TC_03</t>
   </si>
   <si>
@@ -119,7 +125,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: Pra@soon#</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name "Pra@soon#"
 3. Proceed/submit the form</t>
   </si>
@@ -139,7 +145,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: (blank)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Leave candidate name field blank
 3. Proceed/submit the form</t>
   </si>
@@ -159,7 +165,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: "  Prasoon  "</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name "  Prasoon  " (with leading/trailing spaces)
 3. Proceed/submit the form</t>
   </si>
@@ -185,7 +191,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: 300+ character alphabetic string</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter a candidate name exceeding the allowed maximum length
 3. Proceed/submit the form</t>
   </si>
@@ -208,7 +214,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: P</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name "P"
 3. Proceed/submit the form</t>
   </si>
@@ -228,7 +234,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: "Prasoon    Kumar"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name "Prasoon    Kumar" (multiple spaces between words)
 3. Proceed/submit the form</t>
   </si>
@@ -251,7 +257,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: "     "</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name as only spaces
 3. Proceed/submit the form</t>
   </si>
@@ -274,7 +280,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: "PrÃ¤soon" / "à¤ªà¥à¤°à¤¸à¥‚à¤¨"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name with unicode characters
 3. Proceed/submit the form</t>
   </si>
@@ -294,7 +300,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: "Prasoon&lt;tab&gt;&lt;ZWSP&gt;"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Paste candidate name containing hidden/non-printable characters
 3. Proceed/submit the form</t>
   </si>
@@ -317,7 +323,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: "&lt;script&gt;alert(1)&lt;/script&gt;" / "' OR '1'='1"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter candidate name as a script tag or SQL injection string
 3. Proceed/submit the form</t>
   </si>
@@ -340,7 +346,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 9876543210</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number "9876543210"
 3. Proceed/submit the form</t>
   </si>
@@ -363,7 +369,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 987654321</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number "987654321" (9 digits)
 3. Proceed/submit the form</t>
   </si>
@@ -386,7 +392,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 98765432101 (11 digits)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter an 11-digit mobile number
 3. Proceed/submit the form</t>
   </si>
@@ -409,7 +415,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: abcdefghij</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number "abcdefghij"
 3. Proceed/submit the form</t>
   </si>
@@ -429,7 +435,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 98765@#$21</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number "98765@#$21"
 3. Proceed/submit the form</t>
   </si>
@@ -446,7 +452,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: +919876543210</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number "+919876543210"
 3. Proceed/submit the form</t>
   </si>
@@ -466,7 +472,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 0987654321</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2- enter any valid name eg- Prasoon Chauhan
 3. Enter mobile number "0987654321"
 4. enter reference id - 10001556    
@@ -479,6 +485,9 @@
     <t>Accepted. Field value: "0987654321".</t>
   </si>
   <si>
+    <t>P2</t>
+  </si>
+  <si>
     <t>TC_20</t>
   </si>
   <si>
@@ -491,7 +500,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 0000000000</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2- enter any valid name eg- Prasoon Chauhan
 3. Enter mobile number "0000000000"
 4. enter reference id - 10001556    
@@ -516,7 +525,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 98765-43210</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number "98765-43210"
 3. Proceed/submit the form</t>
   </si>
@@ -536,7 +545,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: (blank), Email ID: (blank)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Leave Mobile Number and Email ID both blank
 3. Proceed/submit the form</t>
   </si>
@@ -559,7 +568,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: "९८७६५४३२१०"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number using non-ASCII digit characters
 3. Proceed/submit the form</t>
   </si>
@@ -576,7 +585,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: "&lt;script&gt;alert(1)&lt;/script&gt;" / "' OR '1'='1"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter mobile number as a script tag or SQL injection string
 3. Proceed/submit the form</t>
   </si>
@@ -599,7 +608,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: prasoon@gmail.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "prasoon@gmail.com"
 3. Proceed/submit the form</t>
   </si>
@@ -622,7 +631,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: prasoongmail.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "prasoongmail.com"
 3. Proceed/submit the form</t>
   </si>
@@ -645,7 +654,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: prasoon@gmail</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "prasoon@gmail"
 3. Proceed/submit the form</t>
   </si>
@@ -662,7 +671,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: pra@soon@gmail.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "pra@soon@gmail.com"
 3. Proceed/submit the form</t>
   </si>
@@ -679,7 +688,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: "prasoon kumar@gmail.com"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "prasoon kumar@gmail.com"
 3. Proceed/submit the form</t>
   </si>
@@ -696,7 +705,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: "  prasoon@gmail.com  "</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "  prasoon@gmail.com  " (with leading/trailing spaces)
 3. Proceed/submit the form</t>
   </si>
@@ -710,7 +719,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: (blank), Mobile Number: (blank)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Leave Email ID and Mobile Number both blank
 3. Proceed/submit the form</t>
   </si>
@@ -727,7 +736,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: 250+ character local part + @gmail.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter an email exceeding the allowed maximum length
 3. Proceed/submit the form</t>
   </si>
@@ -747,7 +756,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: "&lt;script&gt;alert(1)&lt;/script&gt;@gmail.com" / "test' OR '1'='1'@gmail.com"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email as a script tag or SQL injection string
 3. Proceed/submit the form</t>
   </si>
@@ -767,7 +776,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: prasoon@mankindpharma.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter any valid name eg- Prasoon Chauhan
 3. Enter email "prasoon@mankindpharma.com"
 4. enter reference id - 10001556
@@ -792,7 +801,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: Prasoon@MANKINDPHARMA.COM</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter any valid name eg- Prasoon Chauhan
 3. Enter email "PRASOON@MANKINDPHARMA.COM"
 4. enter reference id - 10001556
@@ -817,7 +826,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Email ID: prasoon@sub.mankindpharma.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter email "prasoon@sub.mankindpharma.com"
 3. Proceed/submit the form</t>
   </si>
@@ -840,7 +849,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Scenario A: Mobile Number: 9876543210, Email ID: (blank) | Scenario B: Mobile Number: (blank), Email ID: prasoon@gmail.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Fill Candidate Name and Reference ID with valid values
 3. Enter Mobile Number only (leave Email ID blank) and submit - verify no mandatory-field modal appears
 4. Reload, then enter Email ID only (leave Mobile Number blank) and submit - verify no mandatory-field modal appears</t>
@@ -864,7 +873,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Mobile Number: 9876543210, Email ID: prasoon@gmail.com</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Fill Candidate Name and Reference ID with valid values
 3. Enter Mobile Number and Email_id both</t>
   </si>
@@ -887,7 +896,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Candidate Name: Prasoon Test, Reference ID: 10001556, Mobile Number: &lt;fresh 10-digit number&gt;, Email ID: &lt;fresh email&gt;</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Candidate Name, a valid Reference ID, and a freshly-generated Mobile Number and Email
 3. Click Submit
 4. Wait for the result</t>
@@ -896,7 +905,7 @@
     <t>Form should submit successfully and show a "Candidate has been referred successfully!" confirmation (not a validation error, and not a "candidate already exists" prompt)</t>
   </si>
   <si>
-    <t>Submitted with Mobile "9033843903" / Email "prasoon.qa.1789033843903@gmail.com" / Reference ID "10001556" -&gt; success modal: "Candidate has been referred successfully!
+    <t xml:space="preserve">Submitted with Mobile "9033843903" / Email "prasoon.qa.1789033843903@gmail.com" / Reference ID "10001556" -&gt; success modal: "Candidate has been referred successfully!
 You can share the following link with the candidate for registration:".</t>
   </si>
   <si>
@@ -912,7 +921,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | All four fields pre-filled with sample values</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Fill Candidate Name, Mobile Number, Email ID, and Reference ID with sample values
 3. Click Reset
 4. Confirm the "Are you sure to Reset all fields?" prompt by clicking Yes
@@ -937,7 +946,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: 10001556 (known valid), fresh Mobile Number/Email</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Candidate Name, a fresh Mobile Number/Email, and Reference ID "10001556"
 3. Proceed/submit the form</t>
   </si>
@@ -945,7 +954,7 @@
     <t>Reference ID should be accepted and the referral forwarded (e.g. a success confirmation shown)</t>
   </si>
   <si>
-    <t>Mobile "9041170662" / Email "prasoon.qa.1789041170662@gmail.com" -&gt; success modal: "Candidate has been referred successfully!
+    <t xml:space="preserve">Mobile "9041170662" / Email "prasoon.qa.1789041170662@gmail.com" -&gt; success modal: "Candidate has been referred successfully!
 You can share the following link with the candidate for registration:".</t>
   </si>
   <si>
@@ -961,7 +970,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: 12345678 (correct format, not in DB)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "12345678" (valid shape, not a real SAP ID)
 3. Proceed/submit the form</t>
   </si>
@@ -984,7 +993,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: 1000155 (7 digits)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "1000155" (7 digits)
 3. Proceed/submit the form</t>
   </si>
@@ -1007,7 +1016,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: 123456789 (9 digits, truncates to 12345678)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "123456789" (9 digits)
 3. Proceed/submit the form</t>
   </si>
@@ -1030,7 +1039,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: abcdefgh</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "abcdefgh"
 3. Proceed/submit the form</t>
   </si>
@@ -1050,7 +1059,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: 1000@#56</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "1000@#56"
 3. Proceed/submit the form</t>
   </si>
@@ -1067,7 +1076,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: "1000 155"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "1000 155"
 3. Proceed/submit the form</t>
   </si>
@@ -1084,7 +1093,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: 01000155</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID "01000155" (8 digits, leading zero)
 3. Proceed/submit the form</t>
   </si>
@@ -1104,7 +1113,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: (blank)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Leave Reference ID blank
 3. Proceed/submit the form</t>
   </si>
@@ -1124,7 +1133,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Reference ID: "&lt;script&gt;" / "1' OR '1"</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Reference ID as a script tag or SQL injection string
 3. Proceed/submit the form</t>
   </si>
@@ -1147,7 +1156,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Locate the Candidate Name field
 3. Locate the Mobile Number field
 4. Locate the Email ID field
@@ -1172,7 +1181,7 @@
     <t>Verifying that the header logo, page title, subtitle, field labels, button/link text, info notes, and footer copyright text are all present and correctly worded</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Verify the Mankind header logo is visible
 3. Verify the page title "Manager Referral" and subtitle "Complete the form to submit your referral" are present
 4. Verify field labels: Candidate Name, Mobile Number, Email ID, Reference ID (Manager SAP code)
@@ -1199,7 +1208,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral | Name: Prasoon, Email: valid, Reference ID: 10001556</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Enter Candidate Name "Prasoon"
 3. Enter a valid Email ID
 4. Enter Reference ID "10001556"
@@ -1224,7 +1233,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (click "View Manager Referral Report" to reach this view)</t>
   </si>
   <si>
-    <t>1. Open the manager referral link
+    <t xml:space="preserve">1. Open the manager referral link
 2. Click "View Manager Referral Report"
 3. Locate the Reference ID (Manager SAP code) input
 4. Locate the Get Records button
@@ -1249,7 +1258,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: 10001556</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID "10001556"
 3. Click Get Records
 4. Wait for the grid to populate</t>
@@ -1270,7 +1279,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: 12345678</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID "12345678" (valid shape, not a real SAP ID)
 3. Click Get Records</t>
   </si>
@@ -1278,7 +1287,7 @@
     <t>A "No Record Found!" message should be shown and the grid should remain empty</t>
   </si>
   <si>
-    <t>No records shown. Modal text: "×
+    <t xml:space="preserve">No records shown. Modal text: "×
 Information
 No Record Found!
 OK".</t>
@@ -1293,7 +1302,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: 1000155 (7 digits)</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID "1000155" (7 digits)
 3. Click Get Records</t>
   </si>
@@ -1313,7 +1322,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: 122334567 (9 digits)</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID "122334567" (9 digits)
 3. Click Get Records</t>
   </si>
@@ -1327,7 +1336,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: abcdefgh</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID "abcdefgh"
 3. Click Get Records</t>
   </si>
@@ -1341,7 +1350,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: 1000@#56</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID "1000@#56"
 3. Click Get Records</t>
   </si>
@@ -1355,7 +1364,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: (blank)</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Leave Reference ID blank
 3. Click Get Records</t>
   </si>
@@ -1369,12 +1378,12 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report) | Reference ID: "&lt;script&gt;alert(1)&lt;/script&gt;" / "' OR '1'='1"</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Enter Reference ID as a script tag or SQL injection string
 3. Click Get Records</t>
   </si>
   <si>
-    <t>No records shown. Modal text: "×
+    <t xml:space="preserve">No records shown. Modal text: "×
 Information
 No Record Found!
 OK". Secondary input "' OR '1'='1": No records shown. Modal text: "×
@@ -1389,7 +1398,7 @@
     <t>Verifying that typing a value into the Referral date column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's Referral date column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1409,7 +1418,7 @@
     <t>Verifying that typing a value into the iTAP Number column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's iTAP Number column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1426,7 +1435,7 @@
     <t>Verifying that typing a value into the Candidate name column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's Candidate name column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1443,7 +1452,7 @@
     <t>Verifying that typing a value into the Email ID column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's Email ID column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1460,7 +1469,7 @@
     <t>Verifying that typing a value into the Mobile number column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's Mobile number column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1477,7 +1486,7 @@
     <t>Verifying that typing a value into the Aadhaar number column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's Aadhaar number column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1494,7 +1503,7 @@
     <t>Verifying that typing a value into the Initital feedback column filter correctly narrows the grid, that a non-matching value shows zero rows, and that clearing the filter restores the full result set</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load the baseline dataset
 3. Read a real sample value from the first row's Initital feedback column
 4. Type that value into the column's filter and confirm the grid narrows correctly
@@ -1502,7 +1511,7 @@
 6. Clear the filter and confirm the baseline total is restored</t>
   </si>
   <si>
-    <t>Deferred - Initital feedback data does not exist yet; will be tested later per instruction.</t>
+    <t>Not yet automated. (Deferred - Initital feedback data does not exist yet; will be tested later once initial feedback data comes)</t>
   </si>
   <si>
     <t>Pending</t>
@@ -1514,7 +1523,7 @@
     <t>Verifying the leftmost (first page), left (previous page), right (next page), and rightmost (last page) pagination buttons all navigate correctly, and are disabled/enabled at the correct boundaries</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Search Reference ID "10001556" to load a multi-page dataset
 3. On page 1, confirm First/Previous are disabled and Next/Last are enabled
 4. Click Next and confirm the range advances by one page
@@ -1538,7 +1547,7 @@
     <t>link: https://fcadmin100-dev.apps.ap-3a.mendixcloud.com/p/ManagerReferral (via View Manager Referral Report)</t>
   </si>
   <si>
-    <t>1. Open the Manager Referral Report view
+    <t xml:space="preserve">1. Open the Manager Referral Report view
 2. Verify the Mankind header logo is visible
 3. Verify the page title "Manager Referral Report" is present
 4. Verify the "Reference ID (Manager SAP code)" label and "Get Records" button text are present
@@ -1550,15 +1559,6 @@
   </si>
   <si>
     <t>headerLogo: present; title/label/button/footer text: OK; column headers: Referral date, iTAP Number, Candidate name, Email ID, Mobile number, Aadhaar number present, but "Initial feedback" column header is misspelled "Initital feedback" on the live page.</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>P2</t>
   </si>
 </sst>
 </file>
@@ -1567,19 +1567,19 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1909,7 +1909,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="1" customWidth="1"/>
@@ -1921,11 +1921,10 @@
     <col min="8" max="8" width="125.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="50.5703125" style="1" customWidth="1"/>
     <col min="10" max="11" width="12.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1957,1730 +1956,1730 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="I18" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="J28" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="3" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="I47" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="315" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" ht="315" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="225" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" ht="225" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="28" style="1" customWidth="1"/>
@@ -3690,11 +3689,10 @@
     <col min="7" max="7" width="48" style="1" customWidth="1"/>
     <col min="8" max="8" width="35.85546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="46.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3726,590 +3724,590 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="8" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9" ht="105" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="210" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="210" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" ht="165" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="4" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" ht="165" customHeight="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="210" customHeight="1" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" ht="210" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="3" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="165" customHeight="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>442</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>